--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8648,0.0442,0.0907,0.0040</t>
-  </si>
-  <si>
-    <t>0.8751,0.0291,0.0194,0.0115</t>
-  </si>
-  <si>
-    <t>0.9384,0.0115,0.0147,0.0041</t>
-  </si>
-  <si>
-    <t>0.9238,0.0267,0.0133,0.0037</t>
-  </si>
-  <si>
-    <t>0.7969,0.0547,0.0250,0.0195</t>
-  </si>
-  <si>
-    <t>0.8317,0.0450,0.0270,0.0189</t>
-  </si>
-  <si>
-    <t>0.8316,0.0431,0.0350,0.0212</t>
-  </si>
-  <si>
-    <t>0.8793,0.0516,0.0201,0.0057</t>
-  </si>
-  <si>
-    <t>0.6808,0.0526,0.0367,0.0744</t>
-  </si>
-  <si>
-    <t>0.7597,0.0634,0.0327,0.0486</t>
-  </si>
-  <si>
-    <t>0.8767,0.0543,0.0375,0.0038</t>
-  </si>
-  <si>
-    <t>0.7894,0.0497,0.0260,0.0230</t>
-  </si>
-  <si>
-    <t>0.9625,0.0189,0.0096,0.0003</t>
-  </si>
-  <si>
-    <t>0.9029,0.0244,0.0627,0.0009</t>
-  </si>
-  <si>
-    <t>0.9031,0.0343,0.0740,0.0005</t>
-  </si>
-  <si>
-    <t>0.9332,0.0080,0.0732,0.0004</t>
-  </si>
-  <si>
-    <t>0.8781,0.0572,0.0482,0.0026</t>
-  </si>
-  <si>
-    <t>0.2181,0.8555,0.0784,0.0016</t>
-  </si>
-  <si>
-    <t>0.8147,0.1745,0.0402,0.0011</t>
-  </si>
-  <si>
-    <t>0.8780,0.0336,0.0234,0.0073</t>
-  </si>
-  <si>
-    <t>0.2594,0.7799,0.1285,0.0022</t>
-  </si>
-  <si>
-    <t>0.0595,0.9510,0.1054,0.0020</t>
-  </si>
-  <si>
-    <t>0.9778,0.0026,0.0172,0.0001</t>
-  </si>
-  <si>
-    <t>0.9757,0.0077,0.0092,0.0000</t>
-  </si>
-  <si>
-    <t>0.9017,0.0113,0.0991,0.0005</t>
-  </si>
-  <si>
-    <t>0.9470,0.0018,0.0643,0.0003</t>
-  </si>
-  <si>
-    <t>0.9559,0.0017,0.0618,0.0001</t>
-  </si>
-  <si>
-    <t>0.9264,0.0071,0.0600,0.0012</t>
-  </si>
-  <si>
-    <t>0.7978,0.0049,0.3367,0.0004</t>
-  </si>
-  <si>
-    <t>0.5767,0.4321,0.1011,0.0029</t>
-  </si>
-  <si>
-    <t>0.9604,0.0176,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.3267,0.1084,0.7375,0.0051</t>
-  </si>
-  <si>
-    <t>0.8128,0.1742,0.0525,0.0019</t>
-  </si>
-  <si>
-    <t>0.8497,0.0719,0.0264,0.0074</t>
-  </si>
-  <si>
-    <t>0.7482,0.1440,0.1176,0.0166</t>
-  </si>
-  <si>
-    <t>0.7286,0.1784,0.0764,0.0075</t>
-  </si>
-  <si>
-    <t>0.8968,0.0523,0.0346,0.0016</t>
-  </si>
-  <si>
-    <t>0.8761,0.1403,0.0133,0.0006</t>
-  </si>
-  <si>
-    <t>0.9437,0.0019,0.0945,0.0001</t>
-  </si>
-  <si>
-    <t>0.9585,0.0024,0.0410,0.0003</t>
-  </si>
-  <si>
-    <t>0.8796,0.0080,0.1522,0.0005</t>
-  </si>
-  <si>
-    <t>0.9671,0.0035,0.0307,0.0001</t>
-  </si>
-  <si>
-    <t>0.5724,0.5392,0.0249,0.0003</t>
-  </si>
-  <si>
-    <t>0.9724,0.0056,0.0174,0.0002</t>
-  </si>
-  <si>
-    <t>0.9670,0.0106,0.0081,0.0012</t>
-  </si>
-  <si>
-    <t>0.8897,0.1301,0.0086,0.0005</t>
-  </si>
-  <si>
-    <t>0.8988,0.0779,0.0219,0.0012</t>
-  </si>
-  <si>
-    <t>0.9168,0.0770,0.0123,0.0006</t>
-  </si>
-  <si>
-    <t>0.7731,0.0357,0.1566,0.0019</t>
-  </si>
-  <si>
-    <t>0.9595,0.0010,0.0679,0.0001</t>
-  </si>
-  <si>
-    <t>0.9406,0.0056,0.0624,0.0003</t>
-  </si>
-  <si>
-    <t>0.9744,0.0033,0.0188,0.0001</t>
-  </si>
-  <si>
-    <t>0.8690,0.0041,0.2072,0.0006</t>
-  </si>
-  <si>
-    <t>0.8333,0.0172,0.2256,0.0009</t>
-  </si>
-  <si>
-    <t>0.7804,0.0694,0.0475,0.0137</t>
-  </si>
-  <si>
-    <t>0.8671,0.0382,0.0280,0.0115</t>
-  </si>
-  <si>
-    <t>0.8476,0.0570,0.0272,0.0058</t>
-  </si>
-  <si>
-    <t>0.4939,0.1595,0.5172,0.0055</t>
-  </si>
-  <si>
-    <t>0.8052,0.0555,0.0329,0.0168</t>
-  </si>
-  <si>
-    <t>0.8201,0.0568,0.0450,0.0162</t>
-  </si>
-  <si>
-    <t>0.7355,0.1805,0.0307,0.0090</t>
-  </si>
-  <si>
-    <t>0.5079,0.0641,0.4064,0.0004</t>
-  </si>
-  <si>
-    <t>0.7402,0.0209,0.2985,0.0004</t>
-  </si>
-  <si>
-    <t>0.9048,0.0103,0.0966,0.0003</t>
-  </si>
-  <si>
-    <t>0.5854,0.1415,0.2684,0.0005</t>
-  </si>
-  <si>
-    <t>0.4484,0.0097,0.7460,0.0017</t>
-  </si>
-  <si>
-    <t>0.6271,0.4421,0.0455,0.0014</t>
-  </si>
-  <si>
-    <t>0.0570,0.9691,0.0113,0.0002</t>
-  </si>
-  <si>
-    <t>0.9368,0.0197,0.0383,0.0006</t>
-  </si>
-  <si>
-    <t>0.9274,0.0291,0.0222,0.0018</t>
-  </si>
-  <si>
-    <t>0.3278,0.3381,0.5932,0.0050</t>
-  </si>
-  <si>
-    <t>0.5959,0.1175,0.2040,0.0002</t>
-  </si>
-  <si>
-    <t>0.8464,0.0148,0.2039,0.0005</t>
-  </si>
-  <si>
-    <t>0.3046,0.3821,0.3265,0.0004</t>
-  </si>
-  <si>
-    <t>0.6826,0.0943,0.1219,0.0002</t>
-  </si>
-  <si>
-    <t>0.9724,0.0069,0.0084,0.0005</t>
-  </si>
-  <si>
-    <t>0.8470,0.0447,0.0698,0.0083</t>
-  </si>
-  <si>
-    <t>0.9369,0.0209,0.0107,0.0037</t>
-  </si>
-  <si>
-    <t>0.9505,0.0115,0.0144,0.0025</t>
-  </si>
-  <si>
-    <t>0.9479,0.0116,0.0145,0.0014</t>
-  </si>
-  <si>
-    <t>0.9236,0.0247,0.0202,0.0041</t>
-  </si>
-  <si>
-    <t>0.5605,0.2647,0.1297,0.0005</t>
-  </si>
-  <si>
-    <t>0.8938,0.0131,0.1109,0.0001</t>
-  </si>
-  <si>
-    <t>0.8582,0.0074,0.2167,0.0001</t>
-  </si>
-  <si>
-    <t>0.6289,0.1844,0.1157,0.0001</t>
-  </si>
-  <si>
-    <t>0.5175,0.2123,0.2016,0.0003</t>
-  </si>
-  <si>
-    <t>0.8995,0.0150,0.0994,0.0001</t>
-  </si>
-  <si>
-    <t>0.8674,0.0527,0.0285,0.0077</t>
-  </si>
-  <si>
-    <t>0.8002,0.0359,0.0236,0.0260</t>
-  </si>
-  <si>
-    <t>0.8226,0.0410,0.0230,0.0223</t>
-  </si>
-  <si>
-    <t>0.8772,0.0426,0.0180,0.0056</t>
-  </si>
-  <si>
-    <t>0.8440,0.0364,0.0183,0.0222</t>
-  </si>
-  <si>
-    <t>0.7660,0.0603,0.0484,0.0289</t>
-  </si>
-  <si>
-    <t>0.8313,0.0513,0.0322,0.0117</t>
-  </si>
-  <si>
-    <t>0.9045,0.0254,0.0231,0.0064</t>
-  </si>
-  <si>
-    <t>0.8726,0.0422,0.0273,0.0098</t>
-  </si>
-  <si>
-    <t>0.8923,0.0290,0.0185,0.0083</t>
-  </si>
-  <si>
-    <t>0.8356,0.0610,0.0378,0.0082</t>
-  </si>
-  <si>
-    <t>0.8564,0.0350,0.0191,0.0153</t>
-  </si>
-  <si>
-    <t>0.7415,0.0464,0.0188,0.0349</t>
-  </si>
-  <si>
-    <t>0.6991,0.0453,0.0277,0.0443</t>
-  </si>
-  <si>
-    <t>0.7806,0.0538,0.0524,0.0231</t>
-  </si>
-  <si>
-    <t>0.8348,0.0328,0.0176,0.0153</t>
-  </si>
-  <si>
-    <t>0.2280,0.0458,0.8612,0.0013</t>
-  </si>
-  <si>
-    <t>0.7950,0.0317,0.2480,0.0007</t>
-  </si>
-  <si>
-    <t>0.9586,0.0074,0.0291,0.0003</t>
-  </si>
-  <si>
-    <t>0.9314,0.0095,0.0611,0.0002</t>
-  </si>
-  <si>
-    <t>0.5169,0.5716,0.0802,0.0018</t>
-  </si>
-  <si>
-    <t>0.6541,0.4338,0.0477,0.0011</t>
-  </si>
-  <si>
-    <t>0.7713,0.1028,0.0816,0.0094</t>
-  </si>
-  <si>
-    <t>0.6976,0.2488,0.1045,0.0043</t>
-  </si>
-  <si>
-    <t>0.7241,0.2449,0.0448,0.0037</t>
-  </si>
-  <si>
-    <t>0.3020,0.7784,0.0527,0.0015</t>
-  </si>
-  <si>
-    <t>0.7892,0.2177,0.0490,0.0008</t>
-  </si>
-  <si>
-    <t>0.9443,0.0266,0.0091,0.0016</t>
-  </si>
-  <si>
-    <t>0.9516,0.0042,0.0514,0.0001</t>
-  </si>
-  <si>
-    <t>0.9443,0.0186,0.0219,0.0010</t>
-  </si>
-  <si>
-    <t>0.9655,0.0108,0.0117,0.0003</t>
-  </si>
-  <si>
-    <t>0.8540,0.0719,0.0465,0.0093</t>
-  </si>
-  <si>
-    <t>0.8901,0.1392,0.0180,0.0002</t>
-  </si>
-  <si>
-    <t>0.4742,0.7008,0.0310,0.0005</t>
-  </si>
-  <si>
-    <t>0.7934,0.2446,0.0382,0.0006</t>
-  </si>
-  <si>
-    <t>0.1603,0.8814,0.0868,0.0012</t>
-  </si>
-  <si>
-    <t>0.9129,0.0594,0.0198,0.0012</t>
-  </si>
-  <si>
-    <t>0.8045,0.1062,0.0615,0.0055</t>
-  </si>
-  <si>
-    <t>0.8157,0.0970,0.0735,0.0034</t>
-  </si>
-  <si>
-    <t>0.9000,0.0251,0.0133,0.0110</t>
-  </si>
-  <si>
-    <t>0.7824,0.0579,0.0415,0.0320</t>
-  </si>
-  <si>
-    <t>0.8267,0.0260,0.0223,0.0311</t>
-  </si>
-  <si>
-    <t>0.9040,0.0229,0.0219,0.0056</t>
-  </si>
-  <si>
-    <t>0.8230,0.0675,0.0711,0.0077</t>
-  </si>
-  <si>
-    <t>0.8660,0.0707,0.0342,0.0051</t>
-  </si>
-  <si>
-    <t>0.9299,0.0161,0.0071,0.0039</t>
-  </si>
-  <si>
-    <t>0.8655,0.0670,0.0162,0.0047</t>
-  </si>
-  <si>
-    <t>0.9783,0.0040,0.0137,0.0002</t>
-  </si>
-  <si>
-    <t>0.9560,0.0034,0.0528,0.0001</t>
-  </si>
-  <si>
-    <t>0.8893,0.0157,0.0906,0.0001</t>
-  </si>
-  <si>
-    <t>0.9679,0.0030,0.0390,0.0000</t>
-  </si>
-  <si>
-    <t>0.9718,0.0122,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.9300,0.0207,0.0468,0.0005</t>
-  </si>
-  <si>
-    <t>0.9819,0.0021,0.0091,0.0001</t>
-  </si>
-  <si>
-    <t>0.9321,0.0353,0.0157,0.0011</t>
-  </si>
-  <si>
-    <t>0.9719,0.0060,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.9217,0.0131,0.0168,0.0060</t>
-  </si>
-  <si>
-    <t>0.9518,0.0067,0.0135,0.0019</t>
-  </si>
-  <si>
-    <t>0.9128,0.0183,0.0262,0.0054</t>
-  </si>
-  <si>
-    <t>0.6313,0.1728,0.1676,0.0030</t>
-  </si>
-  <si>
-    <t>0.8357,0.1061,0.0412,0.0048</t>
-  </si>
-  <si>
-    <t>0.7118,0.2046,0.1020,0.0053</t>
-  </si>
-  <si>
-    <t>0.9587,0.0101,0.0065,0.0026</t>
-  </si>
-  <si>
-    <t>0.8729,0.0923,0.0203,0.0015</t>
-  </si>
-  <si>
-    <t>0.9140,0.0366,0.0272,0.0021</t>
-  </si>
-  <si>
-    <t>0.8856,0.0467,0.0218,0.0051</t>
-  </si>
-  <si>
-    <t>0.8483,0.0422,0.0270,0.0132</t>
-  </si>
-  <si>
-    <t>0.2616,0.1798,0.7200,0.0157</t>
-  </si>
-  <si>
-    <t>0.8050,0.0388,0.0262,0.0290</t>
-  </si>
-  <si>
-    <t>0.7348,0.1267,0.0412,0.0183</t>
-  </si>
-  <si>
-    <t>0.8138,0.1170,0.0587,0.0039</t>
-  </si>
-  <si>
-    <t>0.9184,0.0426,0.0246,0.0011</t>
-  </si>
-  <si>
-    <t>0.8789,0.0620,0.0469,0.0029</t>
-  </si>
-  <si>
-    <t>0.8167,0.0742,0.0938,0.0033</t>
-  </si>
-  <si>
-    <t>0.8601,0.0962,0.0466,0.0010</t>
-  </si>
-  <si>
-    <t>0.9127,0.0416,0.0220,0.0016</t>
-  </si>
-  <si>
-    <t>0.7673,0.1134,0.0441,0.0093</t>
-  </si>
-  <si>
-    <t>0.8577,0.0411,0.0361,0.0149</t>
-  </si>
-  <si>
-    <t>0.8223,0.0944,0.0298,0.0097</t>
-  </si>
-  <si>
-    <t>0.7996,0.1043,0.0614,0.0082</t>
-  </si>
-  <si>
-    <t>0.7639,0.0523,0.0300,0.0456</t>
-  </si>
-  <si>
-    <t>0.8108,0.0892,0.0401,0.0105</t>
-  </si>
-  <si>
-    <t>0.8458,0.0398,0.0259,0.0148</t>
-  </si>
-  <si>
-    <t>0.8603,0.0358,0.0323,0.0124</t>
-  </si>
-  <si>
-    <t>0.7502,0.1318,0.0617,0.0091</t>
-  </si>
-  <si>
-    <t>0.8876,0.0463,0.0325,0.0059</t>
-  </si>
-  <si>
-    <t>0.8063,0.1443,0.0556,0.0028</t>
-  </si>
-  <si>
-    <t>0.6482,0.1539,0.3183,0.0065</t>
-  </si>
-  <si>
-    <t>0.8668,0.0612,0.0217,0.0046</t>
-  </si>
-  <si>
-    <t>0.8679,0.0438,0.0760,0.0022</t>
-  </si>
-  <si>
-    <t>0.8755,0.0424,0.0296,0.0054</t>
-  </si>
-  <si>
-    <t>0.8395,0.0556,0.0514,0.0062</t>
-  </si>
-  <si>
-    <t>0.2609,0.3229,0.6714,0.0027</t>
-  </si>
-  <si>
-    <t>0.8725,0.0465,0.0326,0.0067</t>
-  </si>
-  <si>
-    <t>0.8116,0.0096,0.2804,0.0010</t>
-  </si>
-  <si>
-    <t>0.8014,0.0129,0.2985,0.0010</t>
-  </si>
-  <si>
-    <t>0.7729,0.0319,0.2759,0.0007</t>
-  </si>
-  <si>
-    <t>0.5582,0.1149,0.2526,0.0010</t>
-  </si>
-  <si>
-    <t>0.8621,0.0108,0.2097,0.0003</t>
-  </si>
-  <si>
-    <t>0.4957,0.0289,0.6370,0.0040</t>
-  </si>
-  <si>
-    <t>0.7303,0.0698,0.2255,0.0014</t>
-  </si>
-  <si>
-    <t>0.9497,0.0101,0.0307,0.0005</t>
-  </si>
-  <si>
-    <t>0.7898,0.0527,0.2126,0.0013</t>
-  </si>
-  <si>
-    <t>0.9447,0.0187,0.0323,0.0002</t>
-  </si>
-  <si>
-    <t>0.9580,0.0139,0.0212,0.0005</t>
-  </si>
-  <si>
-    <t>0.8875,0.0587,0.0610,0.0005</t>
-  </si>
-  <si>
-    <t>0.8685,0.0811,0.0681,0.0005</t>
-  </si>
-  <si>
-    <t>0.9580,0.0273,0.0111,0.0003</t>
-  </si>
-  <si>
-    <t>0.7946,0.0632,0.1549,0.0007</t>
-  </si>
-  <si>
-    <t>0.8642,0.0520,0.0294,0.0076</t>
-  </si>
-  <si>
-    <t>0.7964,0.1176,0.0691,0.0041</t>
-  </si>
-  <si>
-    <t>0.8697,0.0397,0.0248,0.0115</t>
-  </si>
-  <si>
-    <t>0.7906,0.0788,0.0409,0.0116</t>
-  </si>
-  <si>
-    <t>0.8446,0.0614,0.0341,0.0061</t>
-  </si>
-  <si>
-    <t>0.9717,0.0126,0.0103,0.0002</t>
-  </si>
-  <si>
-    <t>0.9086,0.0429,0.0491,0.0005</t>
-  </si>
-  <si>
-    <t>0.9321,0.0199,0.0363,0.0015</t>
-  </si>
-  <si>
-    <t>0.9597,0.0094,0.0205,0.0004</t>
-  </si>
-  <si>
-    <t>0.9132,0.0210,0.0600,0.0006</t>
-  </si>
-  <si>
-    <t>0.8677,0.0220,0.1458,0.0005</t>
-  </si>
-  <si>
-    <t>0.9649,0.0024,0.0314,0.0002</t>
-  </si>
-  <si>
-    <t>0.9658,0.0039,0.0300,0.0002</t>
-  </si>
-  <si>
-    <t>0.9639,0.0035,0.0291,0.0001</t>
-  </si>
-  <si>
-    <t>0.9785,0.0014,0.0247,0.0001</t>
-  </si>
-  <si>
-    <t>0.7726,0.0752,0.0204,0.0181</t>
-  </si>
-  <si>
-    <t>0.8624,0.0215,0.0193,0.0140</t>
-  </si>
-  <si>
-    <t>0.8688,0.0328,0.0254,0.0105</t>
-  </si>
-  <si>
-    <t>0.8790,0.0192,0.0127,0.0211</t>
-  </si>
-  <si>
-    <t>0.8498,0.0572,0.0266,0.0088</t>
-  </si>
-  <si>
-    <t>0.8453,0.0421,0.0247,0.0160</t>
-  </si>
-  <si>
-    <t>0.8041,0.0336,0.0244,0.0327</t>
-  </si>
-  <si>
-    <t>0.8601,0.0198,0.0169,0.0235</t>
-  </si>
-  <si>
-    <t>0.9287,0.0302,0.0167,0.0018</t>
-  </si>
-  <si>
-    <t>0.9108,0.0258,0.0290,0.0022</t>
-  </si>
-  <si>
-    <t>0.7827,0.0858,0.0712,0.0124</t>
-  </si>
-  <si>
-    <t>0.8879,0.0011,0.2178,0.0001</t>
-  </si>
-  <si>
-    <t>0.8402,0.0116,0.2092,0.0011</t>
-  </si>
-  <si>
-    <t>0.9373,0.0052,0.0833,0.0001</t>
-  </si>
-  <si>
-    <t>0.6231,0.0018,0.6854,0.0002</t>
-  </si>
-  <si>
-    <t>0.9063,0.0098,0.1014,0.0007</t>
-  </si>
-  <si>
-    <t>0.5588,0.0067,0.6543,0.0007</t>
-  </si>
-  <si>
-    <t>0.9539,0.0009,0.0564,0.0001</t>
-  </si>
-  <si>
-    <t>0.9183,0.0187,0.0822,0.0003</t>
-  </si>
-  <si>
-    <t>0.9405,0.0074,0.0548,0.0005</t>
-  </si>
-  <si>
-    <t>0.9754,0.0076,0.0082,0.0003</t>
-  </si>
-  <si>
-    <t>0.9428,0.0344,0.0229,0.0004</t>
-  </si>
-  <si>
-    <t>0.7734,0.0898,0.0226,0.0122</t>
-  </si>
-  <si>
-    <t>0.9213,0.0368,0.0121,0.0027</t>
-  </si>
-  <si>
-    <t>0.9408,0.0111,0.0050,0.0067</t>
-  </si>
-  <si>
-    <t>0.8604,0.0512,0.0252,0.0091</t>
-  </si>
-  <si>
-    <t>0.7346,0.1172,0.0292,0.0120</t>
-  </si>
-  <si>
-    <t>0.8956,0.0370,0.0219,0.0050</t>
-  </si>
-  <si>
-    <t>0.6920,0.0638,0.0308,0.0405</t>
-  </si>
-  <si>
-    <t>0.7917,0.1122,0.0390,0.0099</t>
-  </si>
-  <si>
-    <t>0.9667,0.0088,0.0177,0.0002</t>
-  </si>
-  <si>
-    <t>0.8673,0.0062,0.2090,0.0003</t>
-  </si>
-  <si>
-    <t>0.8782,0.0061,0.1972,0.0002</t>
-  </si>
-  <si>
-    <t>0.9018,0.0338,0.0661,0.0003</t>
-  </si>
-  <si>
-    <t>0.5688,0.0352,0.4943,0.0009</t>
-  </si>
-  <si>
-    <t>0.9799,0.0069,0.0055,0.0002</t>
-  </si>
-  <si>
-    <t>0.9504,0.0045,0.0662,0.0002</t>
-  </si>
-  <si>
-    <t>0.9787,0.0008,0.0262,0.0001</t>
-  </si>
-  <si>
-    <t>0.8670,0.0524,0.0283,0.0077</t>
-  </si>
-  <si>
-    <t>0.9394,0.0100,0.0147,0.0037</t>
-  </si>
-  <si>
-    <t>0.8856,0.0204,0.0241,0.0121</t>
-  </si>
-  <si>
-    <t>0.9550,0.0130,0.0116,0.0015</t>
-  </si>
-  <si>
-    <t>0.8389,0.0402,0.0287,0.0186</t>
-  </si>
-  <si>
-    <t>0.8051,0.0663,0.1197,0.0056</t>
+    <t>0.9252,0.0339,0.0232,0.0016</t>
+  </si>
+  <si>
+    <t>0.9129,0.0363,0.0242,0.0029</t>
+  </si>
+  <si>
+    <t>0.8993,0.0224,0.0282,0.0074</t>
+  </si>
+  <si>
+    <t>0.8793,0.0408,0.0119,0.0127</t>
+  </si>
+  <si>
+    <t>0.7956,0.0587,0.0343,0.0135</t>
+  </si>
+  <si>
+    <t>0.8482,0.1082,0.0153,0.0020</t>
+  </si>
+  <si>
+    <t>0.7467,0.0842,0.0450,0.0220</t>
+  </si>
+  <si>
+    <t>0.8570,0.0389,0.0210,0.0107</t>
+  </si>
+  <si>
+    <t>0.7988,0.0473,0.0404,0.0254</t>
+  </si>
+  <si>
+    <t>0.8336,0.0715,0.0164,0.0078</t>
+  </si>
+  <si>
+    <t>0.7436,0.1602,0.0385,0.0095</t>
+  </si>
+  <si>
+    <t>0.7765,0.0916,0.0505,0.0112</t>
+  </si>
+  <si>
+    <t>0.9834,0.0066,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.9323,0.0427,0.0166,0.0008</t>
+  </si>
+  <si>
+    <t>0.9230,0.0120,0.0864,0.0004</t>
+  </si>
+  <si>
+    <t>0.9836,0.0032,0.0096,0.0001</t>
+  </si>
+  <si>
+    <t>0.8822,0.0726,0.0502,0.0007</t>
+  </si>
+  <si>
+    <t>0.4220,0.6472,0.1317,0.0021</t>
+  </si>
+  <si>
+    <t>0.3546,0.6998,0.1638,0.0019</t>
+  </si>
+  <si>
+    <t>0.7478,0.1853,0.0823,0.0057</t>
+  </si>
+  <si>
+    <t>0.6852,0.3405,0.0732,0.0026</t>
+  </si>
+  <si>
+    <t>0.0319,0.9707,0.0631,0.0007</t>
+  </si>
+  <si>
+    <t>0.9758,0.0073,0.0115,0.0001</t>
+  </si>
+  <si>
+    <t>0.9441,0.0154,0.0362,0.0001</t>
+  </si>
+  <si>
+    <t>0.9077,0.0100,0.1178,0.0004</t>
+  </si>
+  <si>
+    <t>0.9664,0.0036,0.0324,0.0002</t>
+  </si>
+  <si>
+    <t>0.9576,0.0157,0.0164,0.0003</t>
+  </si>
+  <si>
+    <t>0.9807,0.0021,0.0162,0.0000</t>
+  </si>
+  <si>
+    <t>0.4794,0.0100,0.7606,0.0006</t>
+  </si>
+  <si>
+    <t>0.9018,0.0468,0.0444,0.0020</t>
+  </si>
+  <si>
+    <t>0.9422,0.0399,0.0087,0.0008</t>
+  </si>
+  <si>
+    <t>0.3144,0.0399,0.7973,0.0033</t>
+  </si>
+  <si>
+    <t>0.9032,0.0757,0.0333,0.0004</t>
+  </si>
+  <si>
+    <t>0.7892,0.0998,0.0482,0.0083</t>
+  </si>
+  <si>
+    <t>0.8799,0.0533,0.0361,0.0061</t>
+  </si>
+  <si>
+    <t>0.8488,0.0722,0.0552,0.0047</t>
+  </si>
+  <si>
+    <t>0.9005,0.0658,0.0246,0.0014</t>
+  </si>
+  <si>
+    <t>0.7878,0.1090,0.0619,0.0010</t>
+  </si>
+  <si>
+    <t>0.9587,0.0017,0.0529,0.0002</t>
+  </si>
+  <si>
+    <t>0.8860,0.0076,0.1180,0.0001</t>
+  </si>
+  <si>
+    <t>0.9267,0.0032,0.1267,0.0003</t>
+  </si>
+  <si>
+    <t>0.9373,0.0120,0.0518,0.0002</t>
+  </si>
+  <si>
+    <t>0.1005,0.9254,0.0377,0.0003</t>
+  </si>
+  <si>
+    <t>0.9596,0.0051,0.0351,0.0003</t>
+  </si>
+  <si>
+    <t>0.9436,0.0355,0.0103,0.0009</t>
+  </si>
+  <si>
+    <t>0.6564,0.3902,0.0567,0.0002</t>
+  </si>
+  <si>
+    <t>0.0664,0.9388,0.0783,0.0004</t>
+  </si>
+  <si>
+    <t>0.7248,0.3451,0.0575,0.0009</t>
+  </si>
+  <si>
+    <t>0.5631,0.0281,0.4623,0.0012</t>
+  </si>
+  <si>
+    <t>0.8532,0.0185,0.1722,0.0005</t>
+  </si>
+  <si>
+    <t>0.9371,0.0087,0.0640,0.0002</t>
+  </si>
+  <si>
+    <t>0.8425,0.0260,0.1932,0.0007</t>
+  </si>
+  <si>
+    <t>0.5891,0.0243,0.5414,0.0003</t>
+  </si>
+  <si>
+    <t>0.8926,0.0108,0.1349,0.0001</t>
+  </si>
+  <si>
+    <t>0.8171,0.0854,0.0779,0.0098</t>
+  </si>
+  <si>
+    <t>0.8608,0.0375,0.0280,0.0157</t>
+  </si>
+  <si>
+    <t>0.8029,0.0377,0.0124,0.0225</t>
+  </si>
+  <si>
+    <t>0.8159,0.0531,0.1587,0.0029</t>
+  </si>
+  <si>
+    <t>0.7834,0.0506,0.0289,0.0271</t>
+  </si>
+  <si>
+    <t>0.7618,0.0955,0.0427,0.0187</t>
+  </si>
+  <si>
+    <t>0.7814,0.0847,0.0463,0.0124</t>
+  </si>
+  <si>
+    <t>0.1945,0.3126,0.4688,0.0002</t>
+  </si>
+  <si>
+    <t>0.4593,0.1660,0.3553,0.0003</t>
+  </si>
+  <si>
+    <t>0.9380,0.0033,0.0680,0.0004</t>
+  </si>
+  <si>
+    <t>0.8589,0.0159,0.1607,0.0003</t>
+  </si>
+  <si>
+    <t>0.5170,0.0209,0.6413,0.0004</t>
+  </si>
+  <si>
+    <t>0.8425,0.1233,0.0383,0.0028</t>
+  </si>
+  <si>
+    <t>0.0181,0.9870,0.0119,0.0001</t>
+  </si>
+  <si>
+    <t>0.9072,0.0495,0.0259,0.0017</t>
+  </si>
+  <si>
+    <t>0.9126,0.0327,0.0166,0.0034</t>
+  </si>
+  <si>
+    <t>0.5534,0.1064,0.4852,0.0032</t>
+  </si>
+  <si>
+    <t>0.8540,0.0570,0.0558,0.0001</t>
+  </si>
+  <si>
+    <t>0.9182,0.0329,0.0479,0.0001</t>
+  </si>
+  <si>
+    <t>0.6327,0.4683,0.0108,0.0000</t>
+  </si>
+  <si>
+    <t>0.8146,0.0481,0.1379,0.0003</t>
+  </si>
+  <si>
+    <t>0.8941,0.0204,0.0709,0.0018</t>
+  </si>
+  <si>
+    <t>0.9040,0.0291,0.0191,0.0062</t>
+  </si>
+  <si>
+    <t>0.9783,0.0040,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.8903,0.0449,0.0301,0.0068</t>
+  </si>
+  <si>
+    <t>0.9544,0.0139,0.0111,0.0024</t>
+  </si>
+  <si>
+    <t>0.9501,0.0224,0.0072,0.0015</t>
+  </si>
+  <si>
+    <t>0.9413,0.0164,0.0333,0.0005</t>
+  </si>
+  <si>
+    <t>0.6138,0.1268,0.1991,0.0002</t>
+  </si>
+  <si>
+    <t>0.6866,0.0999,0.2226,0.0002</t>
+  </si>
+  <si>
+    <t>0.8828,0.0138,0.1230,0.0001</t>
+  </si>
+  <si>
+    <t>0.6219,0.2148,0.1318,0.0002</t>
+  </si>
+  <si>
+    <t>0.7024,0.0773,0.1691,0.0009</t>
+  </si>
+  <si>
+    <t>0.8910,0.0551,0.0166,0.0042</t>
+  </si>
+  <si>
+    <t>0.8888,0.0223,0.0281,0.0101</t>
+  </si>
+  <si>
+    <t>0.8996,0.0246,0.0185,0.0077</t>
+  </si>
+  <si>
+    <t>0.7422,0.0808,0.0235,0.0278</t>
+  </si>
+  <si>
+    <t>0.7924,0.0320,0.0271,0.0337</t>
+  </si>
+  <si>
+    <t>0.8176,0.0436,0.0288,0.0170</t>
+  </si>
+  <si>
+    <t>0.8674,0.0365,0.0396,0.0098</t>
+  </si>
+  <si>
+    <t>0.9043,0.0292,0.0231,0.0066</t>
+  </si>
+  <si>
+    <t>0.8616,0.0412,0.0332,0.0089</t>
+  </si>
+  <si>
+    <t>0.8636,0.0244,0.0252,0.0147</t>
+  </si>
+  <si>
+    <t>0.8563,0.0434,0.0174,0.0121</t>
+  </si>
+  <si>
+    <t>0.8611,0.0317,0.0177,0.0127</t>
+  </si>
+  <si>
+    <t>0.8315,0.0957,0.0231,0.0048</t>
+  </si>
+  <si>
+    <t>0.7581,0.0547,0.0457,0.0378</t>
+  </si>
+  <si>
+    <t>0.8102,0.0792,0.0440,0.0167</t>
+  </si>
+  <si>
+    <t>0.8608,0.0379,0.0436,0.0092</t>
+  </si>
+  <si>
+    <t>0.4532,0.0104,0.7602,0.0008</t>
+  </si>
+  <si>
+    <t>0.9647,0.0052,0.0255,0.0002</t>
+  </si>
+  <si>
+    <t>0.9781,0.0024,0.0112,0.0003</t>
+  </si>
+  <si>
+    <t>0.9688,0.0019,0.0238,0.0003</t>
+  </si>
+  <si>
+    <t>0.7759,0.1725,0.0587,0.0030</t>
+  </si>
+  <si>
+    <t>0.5634,0.4942,0.0699,0.0027</t>
+  </si>
+  <si>
+    <t>0.5688,0.4191,0.1288,0.0060</t>
+  </si>
+  <si>
+    <t>0.4676,0.5345,0.1273,0.0031</t>
+  </si>
+  <si>
+    <t>0.6237,0.3914,0.1212,0.0018</t>
+  </si>
+  <si>
+    <t>0.2320,0.8188,0.1484,0.0021</t>
+  </si>
+  <si>
+    <t>0.7187,0.1508,0.0664,0.0129</t>
+  </si>
+  <si>
+    <t>0.9532,0.0159,0.0135,0.0011</t>
+  </si>
+  <si>
+    <t>0.9556,0.0036,0.0413,0.0002</t>
+  </si>
+  <si>
+    <t>0.9475,0.0160,0.0268,0.0003</t>
+  </si>
+  <si>
+    <t>0.9471,0.0202,0.0281,0.0004</t>
+  </si>
+  <si>
+    <t>0.8969,0.0491,0.0475,0.0008</t>
+  </si>
+  <si>
+    <t>0.6164,0.4113,0.0710,0.0003</t>
+  </si>
+  <si>
+    <t>0.4816,0.6185,0.0340,0.0008</t>
+  </si>
+  <si>
+    <t>0.3405,0.7815,0.0485,0.0006</t>
+  </si>
+  <si>
+    <t>0.0551,0.9233,0.2523,0.0010</t>
+  </si>
+  <si>
+    <t>0.8498,0.1527,0.0332,0.0008</t>
+  </si>
+  <si>
+    <t>0.9161,0.0255,0.0186,0.0061</t>
+  </si>
+  <si>
+    <t>0.8181,0.0967,0.0620,0.0039</t>
+  </si>
+  <si>
+    <t>0.8835,0.0192,0.0235,0.0117</t>
+  </si>
+  <si>
+    <t>0.8946,0.0170,0.0251,0.0098</t>
+  </si>
+  <si>
+    <t>0.8073,0.0603,0.0420,0.0175</t>
+  </si>
+  <si>
+    <t>0.9011,0.0249,0.0192,0.0075</t>
+  </si>
+  <si>
+    <t>0.8710,0.0515,0.0286,0.0089</t>
+  </si>
+  <si>
+    <t>0.8230,0.0445,0.0390,0.0202</t>
+  </si>
+  <si>
+    <t>0.9111,0.0150,0.0129,0.0079</t>
+  </si>
+  <si>
+    <t>0.8610,0.0674,0.0294,0.0065</t>
+  </si>
+  <si>
+    <t>0.7500,0.0563,0.1613,0.0002</t>
+  </si>
+  <si>
+    <t>0.7071,0.0371,0.2733,0.0003</t>
+  </si>
+  <si>
+    <t>0.6440,0.0615,0.3435,0.0002</t>
+  </si>
+  <si>
+    <t>0.9572,0.0031,0.0471,0.0002</t>
+  </si>
+  <si>
+    <t>0.9606,0.0233,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.9238,0.0245,0.0400,0.0007</t>
+  </si>
+  <si>
+    <t>0.9211,0.0303,0.0426,0.0003</t>
+  </si>
+  <si>
+    <t>0.9354,0.0180,0.0369,0.0008</t>
+  </si>
+  <si>
+    <t>0.9577,0.0096,0.0124,0.0012</t>
+  </si>
+  <si>
+    <t>0.8920,0.0202,0.0119,0.0138</t>
+  </si>
+  <si>
+    <t>0.8800,0.0524,0.0166,0.0051</t>
+  </si>
+  <si>
+    <t>0.9454,0.0063,0.0055,0.0062</t>
+  </si>
+  <si>
+    <t>0.4911,0.1619,0.3616,0.0013</t>
+  </si>
+  <si>
+    <t>0.8974,0.0412,0.0185,0.0046</t>
+  </si>
+  <si>
+    <t>0.5899,0.3729,0.1385,0.0069</t>
+  </si>
+  <si>
+    <t>0.8738,0.0181,0.0101,0.0268</t>
+  </si>
+  <si>
+    <t>0.7567,0.1731,0.0777,0.0044</t>
+  </si>
+  <si>
+    <t>0.9096,0.0329,0.0309,0.0031</t>
+  </si>
+  <si>
+    <t>0.9400,0.0296,0.0082,0.0014</t>
+  </si>
+  <si>
+    <t>0.7985,0.0580,0.0246,0.0125</t>
+  </si>
+  <si>
+    <t>0.1056,0.4156,0.8080,0.0158</t>
+  </si>
+  <si>
+    <t>0.8548,0.0504,0.0419,0.0113</t>
+  </si>
+  <si>
+    <t>0.8284,0.0203,0.0142,0.0389</t>
+  </si>
+  <si>
+    <t>0.9340,0.0211,0.0322,0.0007</t>
+  </si>
+  <si>
+    <t>0.9511,0.0135,0.0084,0.0016</t>
+  </si>
+  <si>
+    <t>0.9175,0.0499,0.0273,0.0008</t>
+  </si>
+  <si>
+    <t>0.9173,0.0614,0.0196,0.0011</t>
+  </si>
+  <si>
+    <t>0.9575,0.0128,0.0170,0.0007</t>
+  </si>
+  <si>
+    <t>0.8862,0.0406,0.0440,0.0036</t>
+  </si>
+  <si>
+    <t>0.7993,0.0209,0.0147,0.0620</t>
+  </si>
+  <si>
+    <t>0.8933,0.0312,0.0217,0.0059</t>
+  </si>
+  <si>
+    <t>0.7881,0.0595,0.0201,0.0179</t>
+  </si>
+  <si>
+    <t>0.9017,0.0146,0.0097,0.0123</t>
+  </si>
+  <si>
+    <t>0.8591,0.0180,0.0304,0.0195</t>
+  </si>
+  <si>
+    <t>0.9154,0.0228,0.0129,0.0053</t>
+  </si>
+  <si>
+    <t>0.7572,0.1546,0.0647,0.0076</t>
+  </si>
+  <si>
+    <t>0.8018,0.0636,0.0372,0.0140</t>
+  </si>
+  <si>
+    <t>0.8536,0.0589,0.0371,0.0059</t>
+  </si>
+  <si>
+    <t>0.9108,0.0542,0.0238,0.0018</t>
+  </si>
+  <si>
+    <t>0.8438,0.1087,0.0540,0.0013</t>
+  </si>
+  <si>
+    <t>0.8822,0.0504,0.0160,0.0040</t>
+  </si>
+  <si>
+    <t>0.8353,0.0746,0.0484,0.0077</t>
+  </si>
+  <si>
+    <t>0.9174,0.0236,0.0267,0.0021</t>
+  </si>
+  <si>
+    <t>0.9244,0.0186,0.0231,0.0040</t>
+  </si>
+  <si>
+    <t>0.7418,0.1926,0.0948,0.0045</t>
+  </si>
+  <si>
+    <t>0.0303,0.1795,0.9693,0.0007</t>
+  </si>
+  <si>
+    <t>0.7828,0.1216,0.0361,0.0068</t>
+  </si>
+  <si>
+    <t>0.7492,0.0112,0.3901,0.0007</t>
+  </si>
+  <si>
+    <t>0.9637,0.0029,0.0379,0.0001</t>
+  </si>
+  <si>
+    <t>0.9076,0.0169,0.0944,0.0005</t>
+  </si>
+  <si>
+    <t>0.7164,0.0142,0.3891,0.0006</t>
+  </si>
+  <si>
+    <t>0.9689,0.0012,0.0357,0.0001</t>
+  </si>
+  <si>
+    <t>0.8732,0.0040,0.2015,0.0003</t>
+  </si>
+  <si>
+    <t>0.8551,0.0092,0.2113,0.0001</t>
+  </si>
+  <si>
+    <t>0.9633,0.0100,0.0199,0.0003</t>
+  </si>
+  <si>
+    <t>0.8376,0.0729,0.1014,0.0019</t>
+  </si>
+  <si>
+    <t>0.7621,0.0532,0.2516,0.0009</t>
+  </si>
+  <si>
+    <t>0.9458,0.0118,0.0341,0.0005</t>
+  </si>
+  <si>
+    <t>0.9521,0.0217,0.0187,0.0004</t>
+  </si>
+  <si>
+    <t>0.9252,0.0271,0.0336,0.0008</t>
+  </si>
+  <si>
+    <t>0.9472,0.0208,0.0166,0.0006</t>
+  </si>
+  <si>
+    <t>0.8713,0.0558,0.0591,0.0014</t>
+  </si>
+  <si>
+    <t>0.8766,0.0392,0.0315,0.0061</t>
+  </si>
+  <si>
+    <t>0.8444,0.0781,0.0439,0.0066</t>
+  </si>
+  <si>
+    <t>0.8093,0.0872,0.0718,0.0076</t>
+  </si>
+  <si>
+    <t>0.8829,0.0493,0.0221,0.0055</t>
+  </si>
+  <si>
+    <t>0.8769,0.0294,0.0155,0.0096</t>
+  </si>
+  <si>
+    <t>0.9800,0.0043,0.0085,0.0003</t>
+  </si>
+  <si>
+    <t>0.9669,0.0196,0.0080,0.0003</t>
+  </si>
+  <si>
+    <t>0.9491,0.0127,0.0231,0.0007</t>
+  </si>
+  <si>
+    <t>0.9382,0.0086,0.0555,0.0005</t>
+  </si>
+  <si>
+    <t>0.9651,0.0042,0.0244,0.0002</t>
+  </si>
+  <si>
+    <t>0.3524,0.1167,0.6980,0.0024</t>
+  </si>
+  <si>
+    <t>0.9644,0.0029,0.0262,0.0002</t>
+  </si>
+  <si>
+    <t>0.9860,0.0006,0.0130,0.0000</t>
+  </si>
+  <si>
+    <t>0.9273,0.0046,0.0791,0.0001</t>
+  </si>
+  <si>
+    <t>0.9502,0.0046,0.0434,0.0001</t>
+  </si>
+  <si>
+    <t>0.8829,0.0615,0.0184,0.0043</t>
+  </si>
+  <si>
+    <t>0.8618,0.0578,0.0297,0.0090</t>
+  </si>
+  <si>
+    <t>0.8674,0.0411,0.0202,0.0094</t>
+  </si>
+  <si>
+    <t>0.8116,0.0712,0.0358,0.0138</t>
+  </si>
+  <si>
+    <t>0.8393,0.0407,0.0180,0.0186</t>
+  </si>
+  <si>
+    <t>0.8949,0.0207,0.0170,0.0133</t>
+  </si>
+  <si>
+    <t>0.7537,0.0804,0.0394,0.0248</t>
+  </si>
+  <si>
+    <t>0.8848,0.0310,0.0203,0.0087</t>
+  </si>
+  <si>
+    <t>0.8444,0.0464,0.1614,0.0007</t>
+  </si>
+  <si>
+    <t>0.7691,0.1592,0.0693,0.0054</t>
+  </si>
+  <si>
+    <t>0.8751,0.0832,0.0393,0.0021</t>
+  </si>
+  <si>
+    <t>0.8788,0.0031,0.2178,0.0002</t>
+  </si>
+  <si>
+    <t>0.9251,0.0063,0.0699,0.0010</t>
+  </si>
+  <si>
+    <t>0.8651,0.0208,0.1219,0.0003</t>
+  </si>
+  <si>
+    <t>0.8353,0.0015,0.3859,0.0001</t>
+  </si>
+  <si>
+    <t>0.9133,0.0104,0.0997,0.0002</t>
+  </si>
+  <si>
+    <t>0.1556,0.0197,0.8995,0.0012</t>
+  </si>
+  <si>
+    <t>0.9646,0.0027,0.0417,0.0001</t>
+  </si>
+  <si>
+    <t>0.9163,0.0198,0.0618,0.0006</t>
+  </si>
+  <si>
+    <t>0.9617,0.0105,0.0187,0.0005</t>
+  </si>
+  <si>
+    <t>0.9769,0.0052,0.0090,0.0004</t>
+  </si>
+  <si>
+    <t>0.9597,0.0097,0.0181,0.0007</t>
+  </si>
+  <si>
+    <t>0.8625,0.0462,0.0270,0.0095</t>
+  </si>
+  <si>
+    <t>0.8007,0.0494,0.0732,0.0185</t>
+  </si>
+  <si>
+    <t>0.8391,0.0598,0.0405,0.0077</t>
+  </si>
+  <si>
+    <t>0.8338,0.0440,0.0163,0.0153</t>
+  </si>
+  <si>
+    <t>0.8314,0.0356,0.0143,0.0177</t>
+  </si>
+  <si>
+    <t>0.8496,0.0694,0.0226,0.0074</t>
+  </si>
+  <si>
+    <t>0.8216,0.0324,0.0199,0.0244</t>
+  </si>
+  <si>
+    <t>0.6819,0.0385,0.0198,0.0743</t>
+  </si>
+  <si>
+    <t>0.8773,0.0170,0.1414,0.0004</t>
+  </si>
+  <si>
+    <t>0.5477,0.0425,0.4947,0.0003</t>
+  </si>
+  <si>
+    <t>0.8877,0.0450,0.0385,0.0001</t>
+  </si>
+  <si>
+    <t>0.9558,0.0146,0.0195,0.0002</t>
+  </si>
+  <si>
+    <t>0.8692,0.0095,0.2013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9612,0.0042,0.0168,0.0006</t>
+  </si>
+  <si>
+    <t>0.9671,0.0038,0.0344,0.0001</t>
+  </si>
+  <si>
+    <t>0.9684,0.0024,0.0237,0.0006</t>
+  </si>
+  <si>
+    <t>0.8483,0.0464,0.0433,0.0090</t>
+  </si>
+  <si>
+    <t>0.9400,0.0160,0.0229,0.0020</t>
+  </si>
+  <si>
+    <t>0.8795,0.0278,0.0225,0.0156</t>
+  </si>
+  <si>
+    <t>0.9366,0.0109,0.0101,0.0067</t>
+  </si>
+  <si>
+    <t>0.8992,0.0223,0.0251,0.0072</t>
+  </si>
+  <si>
+    <t>0.9067,0.0308,0.0478,0.0011</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9252,0.0339,0.0232,0.0016</t>
-  </si>
-  <si>
-    <t>0.9129,0.0363,0.0242,0.0029</t>
-  </si>
-  <si>
-    <t>0.8993,0.0224,0.0282,0.0074</t>
-  </si>
-  <si>
-    <t>0.8793,0.0408,0.0119,0.0127</t>
-  </si>
-  <si>
-    <t>0.7956,0.0587,0.0343,0.0135</t>
-  </si>
-  <si>
-    <t>0.8482,0.1082,0.0153,0.0020</t>
-  </si>
-  <si>
-    <t>0.7467,0.0842,0.0450,0.0220</t>
-  </si>
-  <si>
-    <t>0.8570,0.0389,0.0210,0.0107</t>
-  </si>
-  <si>
-    <t>0.7988,0.0473,0.0404,0.0254</t>
-  </si>
-  <si>
-    <t>0.8336,0.0715,0.0164,0.0078</t>
-  </si>
-  <si>
-    <t>0.7436,0.1602,0.0385,0.0095</t>
-  </si>
-  <si>
-    <t>0.7765,0.0916,0.0505,0.0112</t>
-  </si>
-  <si>
-    <t>0.9834,0.0066,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9323,0.0427,0.0166,0.0008</t>
-  </si>
-  <si>
-    <t>0.9230,0.0120,0.0864,0.0004</t>
-  </si>
-  <si>
-    <t>0.9836,0.0032,0.0096,0.0001</t>
-  </si>
-  <si>
-    <t>0.8822,0.0726,0.0502,0.0007</t>
-  </si>
-  <si>
-    <t>0.4220,0.6472,0.1317,0.0021</t>
-  </si>
-  <si>
-    <t>0.3546,0.6998,0.1638,0.0019</t>
-  </si>
-  <si>
-    <t>0.7478,0.1853,0.0823,0.0057</t>
-  </si>
-  <si>
-    <t>0.6852,0.3405,0.0732,0.0026</t>
-  </si>
-  <si>
-    <t>0.0319,0.9707,0.0631,0.0007</t>
-  </si>
-  <si>
-    <t>0.9758,0.0073,0.0115,0.0001</t>
-  </si>
-  <si>
-    <t>0.9441,0.0154,0.0362,0.0001</t>
-  </si>
-  <si>
-    <t>0.9077,0.0100,0.1178,0.0004</t>
-  </si>
-  <si>
-    <t>0.9664,0.0036,0.0324,0.0002</t>
-  </si>
-  <si>
-    <t>0.9576,0.0157,0.0164,0.0003</t>
-  </si>
-  <si>
-    <t>0.9807,0.0021,0.0162,0.0000</t>
-  </si>
-  <si>
-    <t>0.4794,0.0100,0.7606,0.0006</t>
-  </si>
-  <si>
-    <t>0.9018,0.0468,0.0444,0.0020</t>
-  </si>
-  <si>
-    <t>0.9422,0.0399,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.3144,0.0399,0.7973,0.0033</t>
-  </si>
-  <si>
-    <t>0.9032,0.0757,0.0333,0.0004</t>
-  </si>
-  <si>
-    <t>0.7892,0.0998,0.0482,0.0083</t>
-  </si>
-  <si>
-    <t>0.8799,0.0533,0.0361,0.0061</t>
-  </si>
-  <si>
-    <t>0.8488,0.0722,0.0552,0.0047</t>
-  </si>
-  <si>
-    <t>0.9005,0.0658,0.0246,0.0014</t>
-  </si>
-  <si>
-    <t>0.7878,0.1090,0.0619,0.0010</t>
-  </si>
-  <si>
-    <t>0.9587,0.0017,0.0529,0.0002</t>
-  </si>
-  <si>
-    <t>0.8860,0.0076,0.1180,0.0001</t>
-  </si>
-  <si>
-    <t>0.9267,0.0032,0.1267,0.0003</t>
-  </si>
-  <si>
-    <t>0.9373,0.0120,0.0518,0.0002</t>
-  </si>
-  <si>
-    <t>0.1005,0.9254,0.0377,0.0003</t>
-  </si>
-  <si>
-    <t>0.9596,0.0051,0.0351,0.0003</t>
-  </si>
-  <si>
-    <t>0.9436,0.0355,0.0103,0.0009</t>
-  </si>
-  <si>
-    <t>0.6564,0.3902,0.0567,0.0002</t>
-  </si>
-  <si>
-    <t>0.0664,0.9388,0.0783,0.0004</t>
-  </si>
-  <si>
-    <t>0.7248,0.3451,0.0575,0.0009</t>
-  </si>
-  <si>
-    <t>0.5631,0.0281,0.4623,0.0012</t>
-  </si>
-  <si>
-    <t>0.8532,0.0185,0.1722,0.0005</t>
-  </si>
-  <si>
-    <t>0.9371,0.0087,0.0640,0.0002</t>
-  </si>
-  <si>
-    <t>0.8425,0.0260,0.1932,0.0007</t>
-  </si>
-  <si>
-    <t>0.5891,0.0243,0.5414,0.0003</t>
-  </si>
-  <si>
-    <t>0.8926,0.0108,0.1349,0.0001</t>
-  </si>
-  <si>
-    <t>0.8171,0.0854,0.0779,0.0098</t>
-  </si>
-  <si>
-    <t>0.8608,0.0375,0.0280,0.0157</t>
-  </si>
-  <si>
-    <t>0.8029,0.0377,0.0124,0.0225</t>
-  </si>
-  <si>
-    <t>0.8159,0.0531,0.1587,0.0029</t>
-  </si>
-  <si>
-    <t>0.7834,0.0506,0.0289,0.0271</t>
-  </si>
-  <si>
-    <t>0.7618,0.0955,0.0427,0.0187</t>
-  </si>
-  <si>
-    <t>0.7814,0.0847,0.0463,0.0124</t>
-  </si>
-  <si>
-    <t>0.1945,0.3126,0.4688,0.0002</t>
-  </si>
-  <si>
-    <t>0.4593,0.1660,0.3553,0.0003</t>
-  </si>
-  <si>
-    <t>0.9380,0.0033,0.0680,0.0004</t>
-  </si>
-  <si>
-    <t>0.8589,0.0159,0.1607,0.0003</t>
-  </si>
-  <si>
-    <t>0.5170,0.0209,0.6413,0.0004</t>
-  </si>
-  <si>
-    <t>0.8425,0.1233,0.0383,0.0028</t>
-  </si>
-  <si>
-    <t>0.0181,0.9870,0.0119,0.0001</t>
-  </si>
-  <si>
-    <t>0.9072,0.0495,0.0259,0.0017</t>
-  </si>
-  <si>
-    <t>0.9126,0.0327,0.0166,0.0034</t>
-  </si>
-  <si>
-    <t>0.5534,0.1064,0.4852,0.0032</t>
-  </si>
-  <si>
-    <t>0.8540,0.0570,0.0558,0.0001</t>
-  </si>
-  <si>
-    <t>0.9182,0.0329,0.0479,0.0001</t>
-  </si>
-  <si>
-    <t>0.6327,0.4683,0.0108,0.0000</t>
-  </si>
-  <si>
-    <t>0.8146,0.0481,0.1379,0.0003</t>
-  </si>
-  <si>
-    <t>0.8941,0.0204,0.0709,0.0018</t>
-  </si>
-  <si>
-    <t>0.9040,0.0291,0.0191,0.0062</t>
-  </si>
-  <si>
-    <t>0.9783,0.0040,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.8903,0.0449,0.0301,0.0068</t>
-  </si>
-  <si>
-    <t>0.9544,0.0139,0.0111,0.0024</t>
-  </si>
-  <si>
-    <t>0.9501,0.0224,0.0072,0.0015</t>
-  </si>
-  <si>
-    <t>0.9413,0.0164,0.0333,0.0005</t>
-  </si>
-  <si>
-    <t>0.6138,0.1268,0.1991,0.0002</t>
-  </si>
-  <si>
-    <t>0.6866,0.0999,0.2226,0.0002</t>
-  </si>
-  <si>
-    <t>0.8828,0.0138,0.1230,0.0001</t>
-  </si>
-  <si>
-    <t>0.6219,0.2148,0.1318,0.0002</t>
-  </si>
-  <si>
-    <t>0.7024,0.0773,0.1691,0.0009</t>
-  </si>
-  <si>
-    <t>0.8910,0.0551,0.0166,0.0042</t>
-  </si>
-  <si>
-    <t>0.8888,0.0223,0.0281,0.0101</t>
-  </si>
-  <si>
-    <t>0.8996,0.0246,0.0185,0.0077</t>
-  </si>
-  <si>
-    <t>0.7422,0.0808,0.0235,0.0278</t>
-  </si>
-  <si>
-    <t>0.7924,0.0320,0.0271,0.0337</t>
-  </si>
-  <si>
-    <t>0.8176,0.0436,0.0288,0.0170</t>
-  </si>
-  <si>
-    <t>0.8674,0.0365,0.0396,0.0098</t>
-  </si>
-  <si>
-    <t>0.9043,0.0292,0.0231,0.0066</t>
-  </si>
-  <si>
-    <t>0.8616,0.0412,0.0332,0.0089</t>
-  </si>
-  <si>
-    <t>0.8636,0.0244,0.0252,0.0147</t>
-  </si>
-  <si>
-    <t>0.8563,0.0434,0.0174,0.0121</t>
-  </si>
-  <si>
-    <t>0.8611,0.0317,0.0177,0.0127</t>
-  </si>
-  <si>
-    <t>0.8315,0.0957,0.0231,0.0048</t>
-  </si>
-  <si>
-    <t>0.7581,0.0547,0.0457,0.0378</t>
-  </si>
-  <si>
-    <t>0.8102,0.0792,0.0440,0.0167</t>
-  </si>
-  <si>
-    <t>0.8608,0.0379,0.0436,0.0092</t>
-  </si>
-  <si>
-    <t>0.4532,0.0104,0.7602,0.0008</t>
-  </si>
-  <si>
-    <t>0.9647,0.0052,0.0255,0.0002</t>
-  </si>
-  <si>
-    <t>0.9781,0.0024,0.0112,0.0003</t>
-  </si>
-  <si>
-    <t>0.9688,0.0019,0.0238,0.0003</t>
-  </si>
-  <si>
-    <t>0.7759,0.1725,0.0587,0.0030</t>
-  </si>
-  <si>
-    <t>0.5634,0.4942,0.0699,0.0027</t>
-  </si>
-  <si>
-    <t>0.5688,0.4191,0.1288,0.0060</t>
-  </si>
-  <si>
-    <t>0.4676,0.5345,0.1273,0.0031</t>
-  </si>
-  <si>
-    <t>0.6237,0.3914,0.1212,0.0018</t>
-  </si>
-  <si>
-    <t>0.2320,0.8188,0.1484,0.0021</t>
-  </si>
-  <si>
-    <t>0.7187,0.1508,0.0664,0.0129</t>
-  </si>
-  <si>
-    <t>0.9532,0.0159,0.0135,0.0011</t>
-  </si>
-  <si>
-    <t>0.9556,0.0036,0.0413,0.0002</t>
-  </si>
-  <si>
-    <t>0.9475,0.0160,0.0268,0.0003</t>
-  </si>
-  <si>
-    <t>0.9471,0.0202,0.0281,0.0004</t>
-  </si>
-  <si>
-    <t>0.8969,0.0491,0.0475,0.0008</t>
-  </si>
-  <si>
-    <t>0.6164,0.4113,0.0710,0.0003</t>
-  </si>
-  <si>
-    <t>0.4816,0.6185,0.0340,0.0008</t>
-  </si>
-  <si>
-    <t>0.3405,0.7815,0.0485,0.0006</t>
-  </si>
-  <si>
-    <t>0.0551,0.9233,0.2523,0.0010</t>
-  </si>
-  <si>
-    <t>0.8498,0.1527,0.0332,0.0008</t>
-  </si>
-  <si>
-    <t>0.9161,0.0255,0.0186,0.0061</t>
-  </si>
-  <si>
-    <t>0.8181,0.0967,0.0620,0.0039</t>
-  </si>
-  <si>
-    <t>0.8835,0.0192,0.0235,0.0117</t>
-  </si>
-  <si>
-    <t>0.8946,0.0170,0.0251,0.0098</t>
-  </si>
-  <si>
-    <t>0.8073,0.0603,0.0420,0.0175</t>
-  </si>
-  <si>
-    <t>0.9011,0.0249,0.0192,0.0075</t>
-  </si>
-  <si>
-    <t>0.8710,0.0515,0.0286,0.0089</t>
-  </si>
-  <si>
-    <t>0.8230,0.0445,0.0390,0.0202</t>
-  </si>
-  <si>
-    <t>0.9111,0.0150,0.0129,0.0079</t>
-  </si>
-  <si>
-    <t>0.8610,0.0674,0.0294,0.0065</t>
-  </si>
-  <si>
-    <t>0.7500,0.0563,0.1613,0.0002</t>
-  </si>
-  <si>
-    <t>0.7071,0.0371,0.2733,0.0003</t>
-  </si>
-  <si>
-    <t>0.6440,0.0615,0.3435,0.0002</t>
-  </si>
-  <si>
-    <t>0.9572,0.0031,0.0471,0.0002</t>
-  </si>
-  <si>
-    <t>0.9606,0.0233,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.9238,0.0245,0.0400,0.0007</t>
-  </si>
-  <si>
-    <t>0.9211,0.0303,0.0426,0.0003</t>
-  </si>
-  <si>
-    <t>0.9354,0.0180,0.0369,0.0008</t>
-  </si>
-  <si>
-    <t>0.9577,0.0096,0.0124,0.0012</t>
-  </si>
-  <si>
-    <t>0.8920,0.0202,0.0119,0.0138</t>
-  </si>
-  <si>
-    <t>0.8800,0.0524,0.0166,0.0051</t>
-  </si>
-  <si>
-    <t>0.9454,0.0063,0.0055,0.0062</t>
-  </si>
-  <si>
-    <t>0.4911,0.1619,0.3616,0.0013</t>
-  </si>
-  <si>
-    <t>0.8974,0.0412,0.0185,0.0046</t>
-  </si>
-  <si>
-    <t>0.5899,0.3729,0.1385,0.0069</t>
-  </si>
-  <si>
-    <t>0.8738,0.0181,0.0101,0.0268</t>
-  </si>
-  <si>
-    <t>0.7567,0.1731,0.0777,0.0044</t>
-  </si>
-  <si>
-    <t>0.9096,0.0329,0.0309,0.0031</t>
-  </si>
-  <si>
-    <t>0.9400,0.0296,0.0082,0.0014</t>
-  </si>
-  <si>
-    <t>0.7985,0.0580,0.0246,0.0125</t>
-  </si>
-  <si>
-    <t>0.1056,0.4156,0.8080,0.0158</t>
-  </si>
-  <si>
-    <t>0.8548,0.0504,0.0419,0.0113</t>
-  </si>
-  <si>
-    <t>0.8284,0.0203,0.0142,0.0389</t>
-  </si>
-  <si>
-    <t>0.9340,0.0211,0.0322,0.0007</t>
-  </si>
-  <si>
-    <t>0.9511,0.0135,0.0084,0.0016</t>
-  </si>
-  <si>
-    <t>0.9175,0.0499,0.0273,0.0008</t>
-  </si>
-  <si>
-    <t>0.9173,0.0614,0.0196,0.0011</t>
-  </si>
-  <si>
-    <t>0.9575,0.0128,0.0170,0.0007</t>
-  </si>
-  <si>
-    <t>0.8862,0.0406,0.0440,0.0036</t>
-  </si>
-  <si>
-    <t>0.7993,0.0209,0.0147,0.0620</t>
-  </si>
-  <si>
-    <t>0.8933,0.0312,0.0217,0.0059</t>
-  </si>
-  <si>
-    <t>0.7881,0.0595,0.0201,0.0179</t>
-  </si>
-  <si>
-    <t>0.9017,0.0146,0.0097,0.0123</t>
-  </si>
-  <si>
-    <t>0.8591,0.0180,0.0304,0.0195</t>
-  </si>
-  <si>
-    <t>0.9154,0.0228,0.0129,0.0053</t>
-  </si>
-  <si>
-    <t>0.7572,0.1546,0.0647,0.0076</t>
-  </si>
-  <si>
-    <t>0.8018,0.0636,0.0372,0.0140</t>
-  </si>
-  <si>
-    <t>0.8536,0.0589,0.0371,0.0059</t>
-  </si>
-  <si>
-    <t>0.9108,0.0542,0.0238,0.0018</t>
-  </si>
-  <si>
-    <t>0.8438,0.1087,0.0540,0.0013</t>
-  </si>
-  <si>
-    <t>0.8822,0.0504,0.0160,0.0040</t>
-  </si>
-  <si>
-    <t>0.8353,0.0746,0.0484,0.0077</t>
-  </si>
-  <si>
-    <t>0.9174,0.0236,0.0267,0.0021</t>
-  </si>
-  <si>
-    <t>0.9244,0.0186,0.0231,0.0040</t>
-  </si>
-  <si>
-    <t>0.7418,0.1926,0.0948,0.0045</t>
-  </si>
-  <si>
-    <t>0.0303,0.1795,0.9693,0.0007</t>
-  </si>
-  <si>
-    <t>0.7828,0.1216,0.0361,0.0068</t>
-  </si>
-  <si>
-    <t>0.7492,0.0112,0.3901,0.0007</t>
-  </si>
-  <si>
-    <t>0.9637,0.0029,0.0379,0.0001</t>
-  </si>
-  <si>
-    <t>0.9076,0.0169,0.0944,0.0005</t>
-  </si>
-  <si>
-    <t>0.7164,0.0142,0.3891,0.0006</t>
-  </si>
-  <si>
-    <t>0.9689,0.0012,0.0357,0.0001</t>
-  </si>
-  <si>
-    <t>0.8732,0.0040,0.2015,0.0003</t>
-  </si>
-  <si>
-    <t>0.8551,0.0092,0.2113,0.0001</t>
-  </si>
-  <si>
-    <t>0.9633,0.0100,0.0199,0.0003</t>
-  </si>
-  <si>
-    <t>0.8376,0.0729,0.1014,0.0019</t>
-  </si>
-  <si>
-    <t>0.7621,0.0532,0.2516,0.0009</t>
-  </si>
-  <si>
-    <t>0.9458,0.0118,0.0341,0.0005</t>
-  </si>
-  <si>
-    <t>0.9521,0.0217,0.0187,0.0004</t>
-  </si>
-  <si>
-    <t>0.9252,0.0271,0.0336,0.0008</t>
-  </si>
-  <si>
-    <t>0.9472,0.0208,0.0166,0.0006</t>
-  </si>
-  <si>
-    <t>0.8713,0.0558,0.0591,0.0014</t>
-  </si>
-  <si>
-    <t>0.8766,0.0392,0.0315,0.0061</t>
-  </si>
-  <si>
-    <t>0.8444,0.0781,0.0439,0.0066</t>
-  </si>
-  <si>
-    <t>0.8093,0.0872,0.0718,0.0076</t>
-  </si>
-  <si>
-    <t>0.8829,0.0493,0.0221,0.0055</t>
-  </si>
-  <si>
-    <t>0.8769,0.0294,0.0155,0.0096</t>
-  </si>
-  <si>
-    <t>0.9800,0.0043,0.0085,0.0003</t>
-  </si>
-  <si>
-    <t>0.9669,0.0196,0.0080,0.0003</t>
-  </si>
-  <si>
-    <t>0.9491,0.0127,0.0231,0.0007</t>
-  </si>
-  <si>
-    <t>0.9382,0.0086,0.0555,0.0005</t>
-  </si>
-  <si>
-    <t>0.9651,0.0042,0.0244,0.0002</t>
-  </si>
-  <si>
-    <t>0.3524,0.1167,0.6980,0.0024</t>
-  </si>
-  <si>
-    <t>0.9644,0.0029,0.0262,0.0002</t>
-  </si>
-  <si>
-    <t>0.9860,0.0006,0.0130,0.0000</t>
-  </si>
-  <si>
-    <t>0.9273,0.0046,0.0791,0.0001</t>
-  </si>
-  <si>
-    <t>0.9502,0.0046,0.0434,0.0001</t>
-  </si>
-  <si>
-    <t>0.8829,0.0615,0.0184,0.0043</t>
-  </si>
-  <si>
-    <t>0.8618,0.0578,0.0297,0.0090</t>
-  </si>
-  <si>
-    <t>0.8674,0.0411,0.0202,0.0094</t>
-  </si>
-  <si>
-    <t>0.8116,0.0712,0.0358,0.0138</t>
-  </si>
-  <si>
-    <t>0.8393,0.0407,0.0180,0.0186</t>
-  </si>
-  <si>
-    <t>0.8949,0.0207,0.0170,0.0133</t>
-  </si>
-  <si>
-    <t>0.7537,0.0804,0.0394,0.0248</t>
-  </si>
-  <si>
-    <t>0.8848,0.0310,0.0203,0.0087</t>
-  </si>
-  <si>
-    <t>0.8444,0.0464,0.1614,0.0007</t>
-  </si>
-  <si>
-    <t>0.7691,0.1592,0.0693,0.0054</t>
-  </si>
-  <si>
-    <t>0.8751,0.0832,0.0393,0.0021</t>
-  </si>
-  <si>
-    <t>0.8788,0.0031,0.2178,0.0002</t>
-  </si>
-  <si>
-    <t>0.9251,0.0063,0.0699,0.0010</t>
-  </si>
-  <si>
-    <t>0.8651,0.0208,0.1219,0.0003</t>
-  </si>
-  <si>
-    <t>0.8353,0.0015,0.3859,0.0001</t>
-  </si>
-  <si>
-    <t>0.9133,0.0104,0.0997,0.0002</t>
-  </si>
-  <si>
-    <t>0.1556,0.0197,0.8995,0.0012</t>
-  </si>
-  <si>
-    <t>0.9646,0.0027,0.0417,0.0001</t>
-  </si>
-  <si>
-    <t>0.9163,0.0198,0.0618,0.0006</t>
-  </si>
-  <si>
-    <t>0.9617,0.0105,0.0187,0.0005</t>
-  </si>
-  <si>
-    <t>0.9769,0.0052,0.0090,0.0004</t>
-  </si>
-  <si>
-    <t>0.9597,0.0097,0.0181,0.0007</t>
-  </si>
-  <si>
-    <t>0.8625,0.0462,0.0270,0.0095</t>
-  </si>
-  <si>
-    <t>0.8007,0.0494,0.0732,0.0185</t>
-  </si>
-  <si>
-    <t>0.8391,0.0598,0.0405,0.0077</t>
-  </si>
-  <si>
-    <t>0.8338,0.0440,0.0163,0.0153</t>
-  </si>
-  <si>
-    <t>0.8314,0.0356,0.0143,0.0177</t>
-  </si>
-  <si>
-    <t>0.8496,0.0694,0.0226,0.0074</t>
-  </si>
-  <si>
-    <t>0.8216,0.0324,0.0199,0.0244</t>
-  </si>
-  <si>
-    <t>0.6819,0.0385,0.0198,0.0743</t>
-  </si>
-  <si>
-    <t>0.8773,0.0170,0.1414,0.0004</t>
-  </si>
-  <si>
-    <t>0.5477,0.0425,0.4947,0.0003</t>
-  </si>
-  <si>
-    <t>0.8877,0.0450,0.0385,0.0001</t>
-  </si>
-  <si>
-    <t>0.9558,0.0146,0.0195,0.0002</t>
-  </si>
-  <si>
-    <t>0.8692,0.0095,0.2013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9612,0.0042,0.0168,0.0006</t>
-  </si>
-  <si>
-    <t>0.9671,0.0038,0.0344,0.0001</t>
-  </si>
-  <si>
-    <t>0.9684,0.0024,0.0237,0.0006</t>
-  </si>
-  <si>
-    <t>0.8483,0.0464,0.0433,0.0090</t>
-  </si>
-  <si>
-    <t>0.9400,0.0160,0.0229,0.0020</t>
-  </si>
-  <si>
-    <t>0.8795,0.0278,0.0225,0.0156</t>
-  </si>
-  <si>
-    <t>0.9366,0.0109,0.0101,0.0067</t>
-  </si>
-  <si>
-    <t>0.8992,0.0223,0.0251,0.0072</t>
-  </si>
-  <si>
-    <t>0.9067,0.0308,0.0478,0.0011</t>
+    <t>0.9340,0.0153,0.0086,0.0247</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.9767,0.0022,0.0007,0.0094</t>
+  </si>
+  <si>
+    <t>0.1279,0.0022,0.0241,0.8940</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9952,0.0009,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0064,0.0019,0.0019</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0030,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9516,0.0335,0.0150,0.0018</t>
+  </si>
+  <si>
+    <t>0.1938,0.0164,0.8703,0.0007</t>
+  </si>
+  <si>
+    <t>0.1456,0.0337,0.9018,0.0033</t>
+  </si>
+  <si>
+    <t>0.0273,0.0085,0.9770,0.0017</t>
+  </si>
+  <si>
+    <t>0.9608,0.0254,0.0134,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.9979,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.0663,0.9497,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.9935,0.0089,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.9979,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.8742,0.0066,0.1403,0.0031</t>
+  </si>
+  <si>
+    <t>0.5349,0.0054,0.4860,0.0194</t>
+  </si>
+  <si>
+    <t>0.0011,0.0006,0.9941,0.0117</t>
+  </si>
+  <si>
+    <t>0.3532,0.0019,0.7977,0.0041</t>
+  </si>
+  <si>
+    <t>0.3216,0.0018,0.8727,0.0003</t>
+  </si>
+  <si>
+    <t>0.0499,0.0101,0.9581,0.0115</t>
+  </si>
+  <si>
+    <t>0.0021,0.0017,0.9865,0.0305</t>
+  </si>
+  <si>
+    <t>0.8508,0.2598,0.0064,0.0008</t>
+  </si>
+  <si>
+    <t>0.4640,0.0607,0.5839,0.0133</t>
+  </si>
+  <si>
+    <t>0.0034,0.0050,0.9947,0.0036</t>
+  </si>
+  <si>
+    <t>0.0422,0.9529,0.0254,0.0013</t>
+  </si>
+  <si>
+    <t>0.8989,0.0727,0.0199,0.0146</t>
+  </si>
+  <si>
+    <t>0.5613,0.0121,0.5267,0.0102</t>
+  </si>
+  <si>
+    <t>0.7501,0.3575,0.0042,0.0012</t>
+  </si>
+  <si>
+    <t>0.0466,0.9546,0.0664,0.0008</t>
+  </si>
+  <si>
+    <t>0.0316,0.4886,0.4885,0.1077</t>
+  </si>
+  <si>
+    <t>0.0446,0.0066,0.9687,0.0055</t>
+  </si>
+  <si>
+    <t>0.0208,0.0328,0.9811,0.0011</t>
+  </si>
+  <si>
+    <t>0.1615,0.0006,0.9291,0.0024</t>
+  </si>
+  <si>
+    <t>0.0428,0.0557,0.9279,0.0016</t>
+  </si>
+  <si>
+    <t>0.0471,0.9299,0.0281,0.0017</t>
+  </si>
+  <si>
+    <t>0.0140,0.0853,0.9717,0.0062</t>
+  </si>
+  <si>
+    <t>0.0495,0.8834,0.0016,0.1638</t>
+  </si>
+  <si>
+    <t>0.0112,0.9706,0.0144,0.0191</t>
+  </si>
+  <si>
+    <t>0.0008,0.9965,0.0070,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.9953,0.0084,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0331,0.9930,0.0038</t>
+  </si>
+  <si>
+    <t>0.0020,0.0171,0.9958,0.0009</t>
+  </si>
+  <si>
+    <t>0.0320,0.0092,0.9757,0.0045</t>
+  </si>
+  <si>
+    <t>0.1171,0.0021,0.9220,0.0064</t>
+  </si>
+  <si>
+    <t>0.0121,0.0261,0.9779,0.0107</t>
+  </si>
+  <si>
+    <t>0.0428,0.2688,0.8960,0.0301</t>
+  </si>
+  <si>
+    <t>0.9796,0.0185,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9736,0.0128,0.0120,0.0009</t>
+  </si>
+  <si>
+    <t>0.9583,0.0234,0.0145,0.0054</t>
+  </si>
+  <si>
+    <t>0.0220,0.0567,0.9820,0.0066</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9642,0.0652,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9623,0.0627,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0014,0.9338,0.9629,0.0004</t>
+  </si>
+  <si>
+    <t>0.0184,0.0154,0.9828,0.0025</t>
+  </si>
+  <si>
+    <t>0.0143,0.0930,0.9473,0.0364</t>
+  </si>
+  <si>
+    <t>0.0002,0.9748,0.9855,0.0000</t>
+  </si>
+  <si>
+    <t>0.0125,0.0054,0.9819,0.0078</t>
+  </si>
+  <si>
+    <t>0.0504,0.9194,0.0311,0.0029</t>
+  </si>
+  <si>
+    <t>0.0097,0.9882,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.8783,0.0132,0.0851,0.0224</t>
+  </si>
+  <si>
+    <t>0.7754,0.0388,0.2389,0.0083</t>
+  </si>
+  <si>
+    <t>0.0149,0.0127,0.9857,0.0036</t>
+  </si>
+  <si>
+    <t>0.0050,0.9620,0.5089,0.0014</t>
+  </si>
+  <si>
+    <t>0.0099,0.9494,0.2650,0.0012</t>
+  </si>
+  <si>
+    <t>0.0081,0.9742,0.0481,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.9730,0.8601,0.0009</t>
+  </si>
+  <si>
+    <t>0.0036,0.0003,0.0303,0.9906</t>
+  </si>
+  <si>
+    <t>0.0018,0.0012,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0046,0.0012,0.0006,0.9978</t>
+  </si>
+  <si>
+    <t>0.0239,0.0019,0.0091,0.9825</t>
+  </si>
+  <si>
+    <t>0.0050,0.0041,0.0023,0.9951</t>
+  </si>
+  <si>
+    <t>0.0022,0.0024,0.0011,0.9979</t>
+  </si>
+  <si>
+    <t>0.0014,0.9871,0.7084,0.0003</t>
+  </si>
+  <si>
+    <t>0.0618,0.6528,0.7350,0.0093</t>
+  </si>
+  <si>
+    <t>0.0071,0.1762,0.9765,0.0009</t>
+  </si>
+  <si>
+    <t>0.0039,0.9037,0.8848,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9750,0.8945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.8728,0.6619,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9740,0.0404,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9878,0.0127,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0015,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9945,0.0030,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0019,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0116,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0039,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0008,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0019,0.9915,0.0037</t>
+  </si>
+  <si>
+    <t>0.0461,0.0053,0.9810,0.0011</t>
+  </si>
+  <si>
+    <t>0.9555,0.0124,0.0190,0.0049</t>
+  </si>
+  <si>
+    <t>0.1946,0.0015,0.9175,0.0015</t>
+  </si>
+  <si>
+    <t>0.0040,0.9914,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.0073,0.9904,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.9884,0.0019,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.9953,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.0011,0.9965,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.9981,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9638,0.0562,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.7317,0.0254,0.2341,0.0347</t>
+  </si>
+  <si>
+    <t>0.1122,0.0082,0.9420,0.0036</t>
+  </si>
+  <si>
+    <t>0.3742,0.0572,0.2305,0.3178</t>
+  </si>
+  <si>
+    <t>0.7970,0.0157,0.1742,0.0044</t>
+  </si>
+  <si>
+    <t>0.0564,0.1587,0.0353,0.8905</t>
+  </si>
+  <si>
+    <t>0.0044,0.9877,0.0163,0.0031</t>
+  </si>
+  <si>
+    <t>0.0017,0.9893,0.0188,0.0064</t>
+  </si>
+  <si>
+    <t>0.0014,0.9922,0.0037,0.0082</t>
+  </si>
+  <si>
+    <t>0.0028,0.9804,0.1476,0.0042</t>
+  </si>
+  <si>
+    <t>0.0044,0.9902,0.0794,0.0003</t>
+  </si>
+  <si>
+    <t>0.8408,0.2638,0.0068,0.0013</t>
+  </si>
+  <si>
+    <t>0.8950,0.1413,0.0092,0.0022</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0037,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0020,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9857,0.0014,0.0005,0.0080</t>
+  </si>
+  <si>
+    <t>0.9951,0.0006,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0090,0.3142,0.9485,0.0027</t>
+  </si>
+  <si>
+    <t>0.0073,0.8304,0.8937,0.0021</t>
+  </si>
+  <si>
+    <t>0.0050,0.0700,0.9817,0.0006</t>
+  </si>
+  <si>
+    <t>0.0465,0.0148,0.9617,0.0041</t>
+  </si>
+  <si>
+    <t>0.9854,0.0026,0.0060,0.0004</t>
+  </si>
+  <si>
+    <t>0.8477,0.0044,0.1933,0.0023</t>
+  </si>
+  <si>
+    <t>0.1745,0.0028,0.9356,0.0059</t>
+  </si>
+  <si>
+    <t>0.5899,0.2331,0.2355,0.0056</t>
+  </si>
+  <si>
+    <t>0.0329,0.0014,0.0071,0.9792</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0006,0.9997</t>
+  </si>
+  <si>
+    <t>0.0055,0.0057,0.0050,0.9941</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.0015,0.9982</t>
+  </si>
+  <si>
+    <t>0.0037,0.8977,0.8367,0.0024</t>
+  </si>
+  <si>
+    <t>0.9959,0.0005,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.1452,0.9023,0.0045,0.0020</t>
+  </si>
+  <si>
+    <t>0.9792,0.0052,0.0021,0.0092</t>
+  </si>
+  <si>
+    <t>0.2183,0.8535,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.4340,0.0042,0.0296,0.6472</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.0924,0.9621,0.0476</t>
+  </si>
+  <si>
+    <t>0.9472,0.0004,0.0012,0.0522</t>
+  </si>
+  <si>
+    <t>0.8815,0.0019,0.0019,0.1352</t>
+  </si>
+  <si>
+    <t>0.2221,0.7585,0.0044,0.0075</t>
+  </si>
+  <si>
+    <t>0.9548,0.0186,0.0027,0.0080</t>
+  </si>
+  <si>
+    <t>0.9860,0.0069,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.8549,0.0731,0.0639,0.0047</t>
+  </si>
+  <si>
+    <t>0.8935,0.0115,0.1059,0.0011</t>
+  </si>
+  <si>
+    <t>0.9922,0.0055,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0005,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.9954,0.0007,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9944,0.0002,0.0005,0.0030</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9850,0.0106,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9948,0.0012,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.8962,0.0623,0.0012,0.0073</t>
+  </si>
+  <si>
+    <t>0.6271,0.5261,0.0055,0.0006</t>
+  </si>
+  <si>
+    <t>0.5434,0.5729,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.1020,0.0606,0.9560,0.0021</t>
+  </si>
+  <si>
+    <t>0.9925,0.0077,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9644,0.0313,0.0060,0.0011</t>
+  </si>
+  <si>
+    <t>0.9894,0.0077,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9473,0.0509,0.0034,0.0047</t>
+  </si>
+  <si>
+    <t>0.0028,0.0177,0.9965,0.0003</t>
+  </si>
+  <si>
+    <t>0.9703,0.0218,0.0039,0.0042</t>
+  </si>
+  <si>
+    <t>0.0066,0.0019,0.9935,0.0020</t>
+  </si>
+  <si>
+    <t>0.0177,0.0038,0.9657,0.0222</t>
+  </si>
+  <si>
+    <t>0.0350,0.0053,0.9729,0.0106</t>
+  </si>
+  <si>
+    <t>0.0031,0.0356,0.9902,0.0016</t>
+  </si>
+  <si>
+    <t>0.1875,0.0015,0.9330,0.0009</t>
+  </si>
+  <si>
+    <t>0.0883,0.0006,0.9687,0.0011</t>
+  </si>
+  <si>
+    <t>0.0064,0.0218,0.9862,0.0032</t>
+  </si>
+  <si>
+    <t>0.1234,0.0119,0.9028,0.0207</t>
+  </si>
+  <si>
+    <t>0.0556,0.0055,0.9731,0.0039</t>
+  </si>
+  <si>
+    <t>0.2179,0.0138,0.8853,0.0017</t>
+  </si>
+  <si>
+    <t>0.2728,0.1210,0.5172,0.0037</t>
+  </si>
+  <si>
+    <t>0.0627,0.1510,0.8871,0.0028</t>
+  </si>
+  <si>
+    <t>0.3233,0.0952,0.6033,0.0028</t>
+  </si>
+  <si>
+    <t>0.6048,0.0882,0.2016,0.1518</t>
+  </si>
+  <si>
+    <t>0.0709,0.0301,0.9323,0.0163</t>
+  </si>
+  <si>
+    <t>0.0149,0.9785,0.0052,0.0014</t>
+  </si>
+  <si>
+    <t>0.0721,0.9612,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.7316,0.4113,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9767,0.0362,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.5911,0.6055,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.7870,0.1206,0.0169,0.0219</t>
+  </si>
+  <si>
+    <t>0.9482,0.0062,0.0354,0.0022</t>
+  </si>
+  <si>
+    <t>0.8009,0.0145,0.0277,0.1604</t>
+  </si>
+  <si>
+    <t>0.9844,0.0018,0.0091,0.0002</t>
+  </si>
+  <si>
+    <t>0.4129,0.0091,0.5161,0.0821</t>
+  </si>
+  <si>
+    <t>0.0077,0.0055,0.9846,0.0052</t>
+  </si>
+  <si>
+    <t>0.0587,0.5558,0.7072,0.0136</t>
+  </si>
+  <si>
+    <t>0.0594,0.0153,0.9160,0.0427</t>
+  </si>
+  <si>
+    <t>0.0274,0.0031,0.9806,0.0032</t>
+  </si>
+  <si>
+    <t>0.0222,0.2529,0.8559,0.0060</t>
+  </si>
+  <si>
+    <t>0.9871,0.0024,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9973,0.0010,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9725,0.0255,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9911,0.0107,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9597,0.0569,0.0013,0.0016</t>
+  </si>
+  <si>
+    <t>0.9900,0.0076,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9942,0.0027,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0548,0.0072,0.9736,0.0046</t>
+  </si>
+  <si>
+    <t>0.1800,0.7312,0.2179,0.0178</t>
+  </si>
+  <si>
+    <t>0.9216,0.0188,0.0116,0.0263</t>
+  </si>
+  <si>
+    <t>0.0223,0.0024,0.9807,0.0079</t>
+  </si>
+  <si>
+    <t>0.0077,0.0034,0.9549,0.0861</t>
+  </si>
+  <si>
+    <t>0.0271,0.2926,0.8873,0.0106</t>
+  </si>
+  <si>
+    <t>0.0823,0.0094,0.9541,0.0026</t>
+  </si>
+  <si>
+    <t>0.0932,0.0314,0.8940,0.0076</t>
+  </si>
+  <si>
+    <t>0.0032,0.0226,0.9929,0.0027</t>
+  </si>
+  <si>
+    <t>0.0094,0.0086,0.9818,0.0110</t>
+  </si>
+  <si>
+    <t>0.0950,0.1125,0.7881,0.0167</t>
+  </si>
+  <si>
+    <t>0.9394,0.0037,0.0421,0.0036</t>
+  </si>
+  <si>
+    <t>0.8715,0.0361,0.0866,0.0119</t>
+  </si>
+  <si>
+    <t>0.9868,0.0025,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.9940,0.0038,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0029,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0138,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0020,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9861,0.0103,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0307,0.1049,0.8993,0.0164</t>
+  </si>
+  <si>
+    <t>0.0042,0.2302,0.9729,0.0007</t>
+  </si>
+  <si>
+    <t>0.0054,0.0055,0.9908,0.0024</t>
+  </si>
+  <si>
+    <t>0.0471,0.0185,0.9377,0.0086</t>
+  </si>
+  <si>
+    <t>0.0054,0.0035,0.9941,0.0012</t>
+  </si>
+  <si>
+    <t>0.8309,0.0044,0.0726,0.0515</t>
+  </si>
+  <si>
+    <t>0.1269,0.0032,0.9530,0.0024</t>
+  </si>
+  <si>
+    <t>0.2196,0.0074,0.1015,0.6250</t>
+  </si>
+  <si>
+    <t>0.9438,0.0003,0.0023,0.0333</t>
+  </si>
+  <si>
+    <t>0.0197,0.0022,0.0010,0.9916</t>
+  </si>
+  <si>
+    <t>0.1270,0.0013,0.0021,0.9512</t>
+  </si>
+  <si>
+    <t>0.0055,0.0004,0.0011,0.9968</t>
+  </si>
+  <si>
+    <t>0.0228,0.0002,0.0002,0.9946</t>
+  </si>
+  <si>
+    <t>0.9663,0.0055,0.0041,0.0110</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
